--- a/artfynd/A 23222-2022 artfynd.xlsx
+++ b/artfynd/A 23222-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23222-2022 artfynd.xlsx
+++ b/artfynd/A 23222-2022 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>117614611</v>
       </c>
       <c r="B3" t="n">
-        <v>82259</v>
+        <v>82261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23222-2022 artfynd.xlsx
+++ b/artfynd/A 23222-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17277609</v>
+        <v>117614611</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söråsen, Mpd</t>
+          <t>Laxsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609474.5103971093</v>
+        <v>609459</v>
       </c>
       <c r="R2" t="n">
-        <v>6967170.655250326</v>
+        <v>6967244</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,129 +757,18 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>117614611</v>
-      </c>
-      <c r="B3" t="n">
-        <v>82261</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Laxsjön, Mpd</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>609459</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6967244</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Maria Edstam</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23222-2022 artfynd.xlsx
+++ b/artfynd/A 23222-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117614611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>